--- a/artfynd/A 9657-2023 artfynd.xlsx
+++ b/artfynd/A 9657-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122178791</v>
       </c>
       <c r="B2" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>122178790</v>
       </c>
       <c r="B3" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 9657-2023 artfynd.xlsx
+++ b/artfynd/A 9657-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122178791</v>
       </c>
       <c r="B2" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>122178790</v>
       </c>
       <c r="B3" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 9657-2023 artfynd.xlsx
+++ b/artfynd/A 9657-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122178791</v>
+        <v>122178790</v>
       </c>
       <c r="B2" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>6425</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483632</v>
+        <v>483618</v>
       </c>
       <c r="R2" t="n">
-        <v>6949480</v>
+        <v>6949490</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122178790</v>
+        <v>122178791</v>
       </c>
       <c r="B3" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -795,11 +790,6 @@
       <c r="E3" t="n">
         <v>6425</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483618</v>
+        <v>483632</v>
       </c>
       <c r="R3" t="n">
-        <v>6949490</v>
+        <v>6949480</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 9657-2023 artfynd.xlsx
+++ b/artfynd/A 9657-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122178790</v>
+        <v>122178791</v>
       </c>
       <c r="B2" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,6 +693,11 @@
       <c r="E2" t="n">
         <v>6425</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -710,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483618</v>
+        <v>483632</v>
       </c>
       <c r="R2" t="n">
-        <v>6949490</v>
+        <v>6949480</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122178791</v>
+        <v>122178790</v>
       </c>
       <c r="B3" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -790,6 +795,11 @@
       <c r="E3" t="n">
         <v>6425</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -807,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483632</v>
+        <v>483618</v>
       </c>
       <c r="R3" t="n">
-        <v>6949480</v>
+        <v>6949490</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 9657-2023 artfynd.xlsx
+++ b/artfynd/A 9657-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122178791</v>
+        <v>122178790</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483632</v>
+        <v>483618</v>
       </c>
       <c r="R2" t="n">
-        <v>6949480</v>
+        <v>6949490</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122178790</v>
+        <v>122178791</v>
       </c>
       <c r="B3" t="n">
         <v>78656</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483618</v>
+        <v>483632</v>
       </c>
       <c r="R3" t="n">
-        <v>6949490</v>
+        <v>6949480</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 9657-2023 artfynd.xlsx
+++ b/artfynd/A 9657-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>122178790</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -780,16 +775,11 @@
         <v>122178791</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -876,6 +866,200 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122178788</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gillhov, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>483578</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6949427</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122178789</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gillhov, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>483583</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6949432</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9657-2023 artfynd.xlsx
+++ b/artfynd/A 9657-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178790</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178791</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178788</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,8 +1080,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178789</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>